--- a/public/downloads/LandersUnderstanding2020.xlsx
+++ b/public/downloads/LandersUnderstanding2020.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="56">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,16 +169,37 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
+  </si>
+  <si>
     <t>H</t>
   </si>
   <si>
     <t>H2</t>
   </si>
   <si>
-    <t>H4</t>
+    <t>H3</t>
   </si>
   <si>
-    <t>H3</t>
+    <t>H4</t>
   </si>
 </sst>
 </file>
@@ -662,10 +685,10 @@
         <v>94</v>
       </c>
       <c r="N3" s="5">
-        <v>167.8976113796234</v>
+        <v>167897.6113796234</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03217045629040494</v>
+        <v>32.17045629040494</v>
       </c>
       <c r="P3" s="5">
         <v>5219</v>
@@ -712,10 +735,10 @@
         <v>94</v>
       </c>
       <c r="N4" s="5">
-        <v>609.966726064682</v>
+        <v>609966.726064682</v>
       </c>
       <c r="O4" s="4">
-        <v>0.05397935628890991</v>
+        <v>53.97935628890991</v>
       </c>
       <c r="P4" s="5">
         <v>11300</v>
@@ -762,10 +785,10 @@
         <v>94</v>
       </c>
       <c r="N5" s="5">
-        <v>951.2698812484741</v>
+        <v>951269.8812484741</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1370310978462221</v>
+        <v>137.0310978462221</v>
       </c>
       <c r="P5" s="5">
         <v>6942</v>
@@ -812,10 +835,10 @@
         <v>94</v>
       </c>
       <c r="N6" s="5">
-        <v>1207.932188510895</v>
+        <v>1207932.188510895</v>
       </c>
       <c r="O6" s="4">
-        <v>0.0830079843671588</v>
+        <v>83.0079843671588</v>
       </c>
       <c r="P6" s="5">
         <v>14552</v>
@@ -862,10 +885,10 @@
         <v>94</v>
       </c>
       <c r="N7" s="5">
-        <v>1077.139176607132</v>
+        <v>1077139.176607132</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1832492644789268</v>
+        <v>183.2492644789268</v>
       </c>
       <c r="P7" s="5">
         <v>5878</v>
@@ -912,10 +935,10 @@
         <v>94</v>
       </c>
       <c r="N8" s="5">
-        <v>139.183956861496</v>
+        <v>139183.956861496</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01505016834575</v>
+        <v>15.05016834575</v>
       </c>
       <c r="P8" s="5">
         <v>9248</v>
@@ -962,10 +985,10 @@
         <v>94</v>
       </c>
       <c r="N9" s="5">
-        <v>448.4015810489655</v>
+        <v>448401.5810489655</v>
       </c>
       <c r="O9" s="4">
-        <v>0.02937641385278862</v>
+        <v>29.37641385278862</v>
       </c>
       <c r="P9" s="5">
         <v>15264</v>
@@ -1012,10 +1035,10 @@
         <v>94</v>
       </c>
       <c r="N10" s="5">
-        <v>615.6547989845276</v>
+        <v>615654.7989845276</v>
       </c>
       <c r="O10" s="4">
-        <v>0.0821530289544339</v>
+        <v>82.15302895443389</v>
       </c>
       <c r="P10" s="5">
         <v>7494</v>
@@ -1062,10 +1085,10 @@
         <v>94</v>
       </c>
       <c r="N11" s="5">
-        <v>405.5360078811646</v>
+        <v>405536.0078811646</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04061045542571246</v>
+        <v>40.61045542571245</v>
       </c>
       <c r="P11" s="5">
         <v>9986</v>
@@ -1112,10 +1135,10 @@
         <v>94</v>
       </c>
       <c r="N12" s="5">
-        <v>132.9470331668854</v>
+        <v>132947.0331668854</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01903867007974873</v>
+        <v>19.03867007974873</v>
       </c>
       <c r="P12" s="5">
         <v>6983</v>
@@ -1162,10 +1185,10 @@
         <v>94</v>
       </c>
       <c r="N13" s="5">
-        <v>445.2180774211884</v>
+        <v>445218.0774211884</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07141772175508315</v>
+        <v>71.41772175508315</v>
       </c>
       <c r="P13" s="5">
         <v>6234</v>
@@ -1212,10 +1235,10 @@
         <v>94</v>
       </c>
       <c r="N14" s="5">
-        <v>686.2914917469025</v>
+        <v>686291.4917469025</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2660044541654661</v>
+        <v>266.0044541654661</v>
       </c>
       <c r="P14" s="5">
         <v>2580</v>
@@ -1262,10 +1285,10 @@
         <v>94</v>
       </c>
       <c r="N15" s="5">
-        <v>3542.38223195076</v>
+        <v>3542382.23195076</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2697724645457893</v>
+        <v>269.7724645457894</v>
       </c>
       <c r="P15" s="5">
         <v>13131</v>
@@ -1312,10 +1335,10 @@
         <v>94</v>
       </c>
       <c r="N16" s="5">
-        <v>303.1804075241089</v>
+        <v>303180.4075241089</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1000595404369996</v>
+        <v>100.0595404369996</v>
       </c>
       <c r="P16" s="5">
         <v>3030</v>
@@ -1362,10 +1385,10 @@
         <v>94</v>
       </c>
       <c r="N17" s="5">
-        <v>633.2826075553894</v>
+        <v>633282.6075553894</v>
       </c>
       <c r="O17" s="4">
-        <v>0.0968766418166421</v>
+        <v>96.87664181664211</v>
       </c>
       <c r="P17" s="5">
         <v>6537</v>
@@ -1393,7 +1416,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1404,9 +1427,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1440,8 +1469,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1463,25 +1500,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2568767885695105</v>
+        <v>0.3196715649670389</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2394009576558705</v>
+        <v>0.3022846986665534</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2408201083492189</v>
+        <v>0.3001057772792698</v>
       </c>
       <c r="E3" s="4">
-        <v>82.52859385512453</v>
+        <v>89.12461687971884</v>
       </c>
       <c r="F3" s="4">
-        <v>86.80495120092486</v>
+        <v>90.82528210044964</v>
       </c>
       <c r="G3" s="5">
         <v>91</v>
@@ -1496,27 +1551,45 @@
         <v>12</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2993017945856602</v>
+      </c>
+      <c r="O3" s="5">
+        <v>79</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.08806409816207127</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04085295962716005</v>
+      </c>
+      <c r="R3" s="5">
+        <v>79</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2470753050286643</v>
+        <v>0.2437046173875945</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2470753050286643</v>
+        <v>0.2437046173875945</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2444291579700675</v>
+        <v>0.2416405087687474</v>
       </c>
       <c r="E4" s="4">
         <v>100</v>
@@ -1545,19 +1618,35 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2437046173875945</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2437046173875945</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6867379026628022</v>
+        <v>0.421519007225676</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6867379026628022</v>
+        <v>0.421519007225676</v>
       </c>
       <c r="D5" s="4">
-        <v>0.6814528529408115</v>
+        <v>0.4184228442974032</v>
       </c>
       <c r="E5" s="4">
         <v>100</v>
@@ -1586,19 +1675,35 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.421519007225676</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.421519007225676</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.4006995911172755</v>
+        <v>0.6057349674054997</v>
       </c>
       <c r="C6" s="4">
-        <v>0.4006995911172755</v>
+        <v>0.6057349674054997</v>
       </c>
       <c r="D6" s="4">
-        <v>0.3967563988916698</v>
+        <v>0.6016067501677913</v>
       </c>
       <c r="E6" s="4">
         <v>100</v>
@@ -1627,9 +1732,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.6057349674054997</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.6057349674054997</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1640,6 +1761,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1647,7 +1769,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1658,9 +1780,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1694,8 +1822,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1717,60 +1853,96 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3035786115397519</v>
+        <v>0.4107293980856612</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2973084006326762</v>
+        <v>0.4159873751647689</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2947372828743348</v>
+        <v>0.3780177021296857</v>
       </c>
       <c r="E3" s="4">
-        <v>88.39762278537789</v>
+        <v>80.48366599387005</v>
       </c>
       <c r="F3" s="4">
-        <v>91.43299653366908</v>
+        <v>82.32981783317355</v>
       </c>
       <c r="G3" s="5">
         <v>91</v>
       </c>
       <c r="H3" s="5">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J3" s="5">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K3" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3" s="5">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.4123078265649519</v>
+      </c>
+      <c r="O3" s="5">
+        <v>67</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.127360857029821</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.07246281092397719</v>
+      </c>
+      <c r="R3" s="5">
+        <v>67</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2606266353515601</v>
+        <v>0.204924902716062</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2606266353515601</v>
+        <v>0.204924902716062</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2588451717285132</v>
+        <v>0.203251204290769</v>
       </c>
       <c r="E4" s="4">
         <v>100</v>
@@ -1799,19 +1971,35 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.204924902716062</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.204924902716062</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.7101382516503918</v>
+        <v>0.3112133092181395</v>
       </c>
       <c r="C5" s="4">
-        <v>0.7101382516503918</v>
+        <v>0.3112133092181395</v>
       </c>
       <c r="D5" s="4">
-        <v>0.706575324404298</v>
+        <v>0.3087027615802</v>
       </c>
       <c r="E5" s="4">
         <v>100</v>
@@ -1840,19 +2028,35 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3112133092181395</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3112133092181395</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.471009308745117</v>
+        <v>0.3374852441430676</v>
       </c>
       <c r="C6" s="4">
-        <v>0.471009308745117</v>
+        <v>0.3374852441430676</v>
       </c>
       <c r="D6" s="4">
-        <v>0.4683371133105467</v>
+        <v>0.3341378472924816</v>
       </c>
       <c r="E6" s="4">
         <v>100</v>
@@ -1881,9 +2085,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.3374852441430676</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.3374852441430676</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1894,6 +2114,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1901,7 +2122,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1912,9 +2133,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1948,8 +2175,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1971,60 +2206,96 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2871606234857069</v>
+        <v>0.2568767885695105</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2872617564407915</v>
+        <v>0.2394009576558705</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2815665742075438</v>
+        <v>0.2408201083492189</v>
       </c>
       <c r="E3" s="4">
-        <v>85.57299843014124</v>
+        <v>82.52859385512453</v>
       </c>
       <c r="F3" s="4">
-        <v>88.67529562160391</v>
+        <v>86.80495120092486</v>
       </c>
       <c r="G3" s="5">
         <v>91</v>
       </c>
       <c r="H3" s="5">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.233914099630112</v>
+      </c>
+      <c r="O3" s="5">
+        <v>79</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1200300971319361</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08176742701258868</v>
+      </c>
+      <c r="R3" s="5">
+        <v>79</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.264525732794187</v>
+        <v>0.2470753050286643</v>
       </c>
       <c r="C4" s="4">
-        <v>0.264525732794187</v>
+        <v>0.2470753050286643</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2617090557006811</v>
+        <v>0.2444291579700675</v>
       </c>
       <c r="E4" s="4">
         <v>100</v>
@@ -2053,19 +2324,35 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2470753050286643</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2470753050286643</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.746609618532716</v>
+        <v>0.4006995911172755</v>
       </c>
       <c r="C5" s="4">
-        <v>0.746609618532716</v>
+        <v>0.4006995911172755</v>
       </c>
       <c r="D5" s="4">
-        <v>0.7412089608789074</v>
+        <v>0.3967563988916698</v>
       </c>
       <c r="E5" s="4">
         <v>100</v>
@@ -2094,19 +2381,35 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4006995911172755</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4006995911172755</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.4733799046771239</v>
+        <v>0.6867379026628022</v>
       </c>
       <c r="C6" s="4">
-        <v>0.4733799046771239</v>
+        <v>0.6867379026628022</v>
       </c>
       <c r="D6" s="4">
-        <v>0.4693322724597166</v>
+        <v>0.6814528529408115</v>
       </c>
       <c r="E6" s="4">
         <v>100</v>
@@ -2135,9 +2438,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.6867379026628022</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.6867379026628022</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2148,6 +2467,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2155,7 +2475,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2166,9 +2486,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2202,8 +2528,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2225,60 +2559,96 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4520452378092619</v>
+        <v>0.3035786115397519</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4468912357492944</v>
+        <v>0.2973084006326762</v>
       </c>
       <c r="D3" s="4">
-        <v>0.44016627314409</v>
+        <v>0.2947372828743348</v>
       </c>
       <c r="E3" s="4">
-        <v>85.08185691859158</v>
+        <v>88.39762278537789</v>
       </c>
       <c r="F3" s="4">
-        <v>90.69990412272347</v>
+        <v>91.43299653366908</v>
       </c>
       <c r="G3" s="5">
         <v>91</v>
       </c>
       <c r="H3" s="5">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2939896287584804</v>
+      </c>
+      <c r="O3" s="5">
+        <v>85</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.09285420642672755</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06479192859970942</v>
+      </c>
+      <c r="R3" s="5">
+        <v>85</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.03017219046630615</v>
+        <v>0.2606266353515601</v>
       </c>
       <c r="C4" s="4">
-        <v>0.03017219046630615</v>
+        <v>0.2606266353515601</v>
       </c>
       <c r="D4" s="4">
-        <v>0.02925237158813232</v>
+        <v>0.2588451717285132</v>
       </c>
       <c r="E4" s="4">
         <v>100</v>
@@ -2307,19 +2677,35 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2606266353515601</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2606266353515601</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.02869408355957148</v>
+        <v>0.471009308745117</v>
       </c>
       <c r="C5" s="4">
-        <v>0.02869408355957148</v>
+        <v>0.471009308745117</v>
       </c>
       <c r="D5" s="4">
-        <v>0.02685635315185664</v>
+        <v>0.4683371133105467</v>
       </c>
       <c r="E5" s="4">
         <v>100</v>
@@ -2348,19 +2734,35 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.471009308745117</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.471009308745117</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.05190044109985337</v>
+        <v>0.7101382516503918</v>
       </c>
       <c r="C6" s="4">
-        <v>0.05190044109985337</v>
+        <v>0.7101382516503918</v>
       </c>
       <c r="D6" s="4">
-        <v>0.05052071278259262</v>
+        <v>0.706575324404298</v>
       </c>
       <c r="E6" s="4">
         <v>100</v>
@@ -2389,9 +2791,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.7101382516503918</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.7101382516503918</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2402,6 +2820,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2409,7 +2828,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2420,9 +2839,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2456,8 +2881,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2479,60 +2912,96 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1167697581807395</v>
+        <v>0.2871606234857069</v>
       </c>
       <c r="C3" s="4">
-        <v>0.09367336922352022</v>
+        <v>0.2872617564407915</v>
       </c>
       <c r="D3" s="4">
-        <v>0.09317204783988633</v>
+        <v>0.2815665742075438</v>
       </c>
       <c r="E3" s="4">
-        <v>97.34245346490218</v>
+        <v>85.57299843014124</v>
       </c>
       <c r="F3" s="4">
-        <v>96.87980922880385</v>
+        <v>88.67529562160391</v>
       </c>
       <c r="G3" s="5">
         <v>91</v>
       </c>
       <c r="H3" s="5">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2836016833318286</v>
+      </c>
+      <c r="O3" s="5">
+        <v>80</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.08193265541058421</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05096215897773898</v>
+      </c>
+      <c r="R3" s="5">
+        <v>80</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5998965416339841</v>
+        <v>0.264525732794187</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5998965416339841</v>
+        <v>0.264525732794187</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5981753979114499</v>
+        <v>0.2617090557006811</v>
       </c>
       <c r="E4" s="4">
         <v>100</v>
@@ -2561,19 +3030,35 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.264525732794187</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.264525732794187</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.336650734412727</v>
+        <v>0.4733799046771239</v>
       </c>
       <c r="C5" s="4">
-        <v>1.336650734412727</v>
+        <v>0.4733799046771239</v>
       </c>
       <c r="D5" s="4">
-        <v>1.333208819496688</v>
+        <v>0.4693322724597166</v>
       </c>
       <c r="E5" s="4">
         <v>100</v>
@@ -2602,19 +3087,35 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4733799046771239</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4733799046771239</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.9642053193347149</v>
+        <v>0.746609618532716</v>
       </c>
       <c r="C6" s="4">
-        <v>0.9642053193347149</v>
+        <v>0.746609618532716</v>
       </c>
       <c r="D6" s="4">
-        <v>0.9616237974660091</v>
+        <v>0.7412089608789074</v>
       </c>
       <c r="E6" s="4">
         <v>100</v>
@@ -2643,9 +3144,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.746609618532716</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.746609618532716</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2656,6 +3173,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2663,7 +3181,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2674,9 +3192,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2710,8 +3234,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2733,60 +3265,96 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3937763564213826</v>
+        <v>0.4520452378092619</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3902253133510657</v>
+        <v>0.4468912357492944</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3888743033243781</v>
+        <v>0.44016627314409</v>
       </c>
       <c r="E3" s="4">
-        <v>84.91066756372868</v>
+        <v>85.08185691859158</v>
       </c>
       <c r="F3" s="4">
-        <v>89.78108021732251</v>
+        <v>90.69990412272347</v>
       </c>
       <c r="G3" s="5">
         <v>91</v>
       </c>
       <c r="H3" s="5">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.4463232564121774</v>
+      </c>
+      <c r="O3" s="5">
+        <v>89</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.05484772101337667</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05079766815826967</v>
+      </c>
+      <c r="R3" s="5">
+        <v>89</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.04243200162925476</v>
+        <v>0.03017219046630615</v>
       </c>
       <c r="C4" s="4">
-        <v>0.04243200162925476</v>
+        <v>0.03017219046630615</v>
       </c>
       <c r="D4" s="4">
-        <v>0.04004732409991973</v>
+        <v>0.02925237158813232</v>
       </c>
       <c r="E4" s="4">
         <v>100</v>
@@ -2815,19 +3383,35 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.03017219046630615</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.03017219046630615</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1922284864068615</v>
+        <v>0.05190044109985337</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1922284864068615</v>
+        <v>0.05190044109985337</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1874590419412243</v>
+        <v>0.05052071278259262</v>
       </c>
       <c r="E5" s="4">
         <v>100</v>
@@ -2856,19 +3440,35 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.05190044109985337</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.05190044109985337</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.1080928689734648</v>
+        <v>0.02869408355957148</v>
       </c>
       <c r="C6" s="4">
-        <v>0.1080928689734648</v>
+        <v>0.02869408355957148</v>
       </c>
       <c r="D6" s="4">
-        <v>0.1045160836474608</v>
+        <v>0.02685635315185664</v>
       </c>
       <c r="E6" s="4">
         <v>100</v>
@@ -2897,9 +3497,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.02869408355957148</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.02869408355957148</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2910,6 +3526,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2917,7 +3534,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2928,9 +3545,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2964,8 +3587,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2987,60 +3618,96 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1085700287280945</v>
+        <v>0.1167697581807395</v>
       </c>
       <c r="C3" s="4">
-        <v>0.0826847675495793</v>
+        <v>0.09367336922352022</v>
       </c>
       <c r="D3" s="4">
-        <v>0.08038889774336967</v>
+        <v>0.09317204783988633</v>
       </c>
       <c r="E3" s="4">
-        <v>95.54160125588687</v>
+        <v>97.34245346490218</v>
       </c>
       <c r="F3" s="4">
-        <v>92.62322688497089</v>
+        <v>96.87980922880385</v>
       </c>
       <c r="G3" s="5">
         <v>91</v>
       </c>
       <c r="H3" s="5">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.0872512832354172</v>
+      </c>
+      <c r="O3" s="5">
+        <v>87</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.06578202343315963</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.03632981755718188</v>
+      </c>
+      <c r="R3" s="5">
+        <v>87</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6196457360176053</v>
+        <v>0.5998965416339841</v>
       </c>
       <c r="C4" s="4">
-        <v>0.6196457360176053</v>
+        <v>0.5998965416339841</v>
       </c>
       <c r="D4" s="4">
-        <v>0.6178747032073941</v>
+        <v>0.5981753979114499</v>
       </c>
       <c r="E4" s="4">
         <v>100</v>
@@ -3069,19 +3736,35 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5998965416339841</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5998965416339841</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.369171460735854</v>
+        <v>0.9642053193347149</v>
       </c>
       <c r="C5" s="4">
-        <v>1.369171460735854</v>
+        <v>0.9642053193347149</v>
       </c>
       <c r="D5" s="4">
-        <v>1.365629514324722</v>
+        <v>0.9616237974660091</v>
       </c>
       <c r="E5" s="4">
         <v>100</v>
@@ -3110,19 +3793,35 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.9642053193347149</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.9642053193347149</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.9948676771418743</v>
+        <v>1.336650734412727</v>
       </c>
       <c r="C6" s="4">
-        <v>0.9948676771418743</v>
+        <v>1.336650734412727</v>
       </c>
       <c r="D6" s="4">
-        <v>0.9922107255952053</v>
+        <v>1.333208819496688</v>
       </c>
       <c r="E6" s="4">
         <v>100</v>
@@ -3151,9 +3850,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.336650734412727</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>1.336650734412727</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3164,6 +3879,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3171,7 +3887,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3182,9 +3898,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3218,8 +3940,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3241,60 +3971,96 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3215216194726652</v>
+        <v>0.3937763564213826</v>
       </c>
       <c r="C3" s="4">
-        <v>0.304270995155191</v>
+        <v>0.3902253133510657</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3021297965935674</v>
+        <v>0.3888743033243781</v>
       </c>
       <c r="E3" s="4">
-        <v>84.2943111310459</v>
+        <v>84.91066756372868</v>
       </c>
       <c r="F3" s="4">
-        <v>88.10162991371092</v>
+        <v>89.78108021732251</v>
       </c>
       <c r="G3" s="5">
         <v>91</v>
       </c>
       <c r="H3" s="5">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3899699117785244</v>
+      </c>
+      <c r="O3" s="5">
+        <v>83</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.06929573381371948</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.03376975661897948</v>
+      </c>
+      <c r="R3" s="5">
+        <v>83</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1749163184551215</v>
+        <v>0.04243200162925476</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1749163184551215</v>
+        <v>0.04243200162925476</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1739942495016074</v>
+        <v>0.04004732409991973</v>
       </c>
       <c r="E4" s="4">
         <v>100</v>
@@ -3323,19 +4089,35 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.04243200162925476</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.04243200162925476</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.512232234346925</v>
+        <v>0.1080928689734648</v>
       </c>
       <c r="C5" s="4">
-        <v>0.512232234346925</v>
+        <v>0.1080928689734648</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5103884242654431</v>
+        <v>0.1045160836474608</v>
       </c>
       <c r="E5" s="4">
         <v>100</v>
@@ -3364,19 +4146,35 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1080928689734648</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1080928689734648</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.3239682859675597</v>
+        <v>0.1922284864068615</v>
       </c>
       <c r="C6" s="4">
-        <v>0.3239682859675597</v>
+        <v>0.1922284864068615</v>
       </c>
       <c r="D6" s="4">
-        <v>0.3225853389994811</v>
+        <v>0.1874590419412243</v>
       </c>
       <c r="E6" s="4">
         <v>100</v>
@@ -3405,9 +4203,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1922284864068615</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1922284864068615</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3418,12 +4232,1576 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.1085700287280945</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.0826847675495793</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.08038889774336967</v>
+      </c>
+      <c r="E3" s="4">
+        <v>95.54160125588687</v>
+      </c>
+      <c r="F3" s="4">
+        <v>92.62322688497089</v>
+      </c>
+      <c r="G3" s="5">
+        <v>91</v>
+      </c>
+      <c r="H3" s="5">
+        <v>79</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>12</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>12</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.07525547677357627</v>
+      </c>
+      <c r="O3" s="5">
+        <v>79</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.07013844041090508</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.03841546961458903</v>
+      </c>
+      <c r="R3" s="5">
+        <v>79</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.6196457360176053</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.6196457360176053</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.6178747032073941</v>
+      </c>
+      <c r="E4" s="4">
+        <v>100</v>
+      </c>
+      <c r="F4" s="4">
+        <v>100</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6196457360176053</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6196457360176053</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.9948676771418743</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.9948676771418743</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.9922107255952053</v>
+      </c>
+      <c r="E5" s="4">
+        <v>100</v>
+      </c>
+      <c r="F5" s="4">
+        <v>100</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.9948676771418743</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.9948676771418743</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
+        <v>1.369171460735854</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1.369171460735854</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1.365629514324722</v>
+      </c>
+      <c r="E6" s="4">
+        <v>100</v>
+      </c>
+      <c r="F6" s="4">
+        <v>100</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.369171460735854</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>1.369171460735854</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.3215216194726652</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.304270995155191</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.3021297965935674</v>
+      </c>
+      <c r="E3" s="4">
+        <v>84.2943111310459</v>
+      </c>
+      <c r="F3" s="4">
+        <v>88.10162991371092</v>
+      </c>
+      <c r="G3" s="5">
+        <v>91</v>
+      </c>
+      <c r="H3" s="5">
+        <v>79</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>12</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>12</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.3026601245750693</v>
+      </c>
+      <c r="O3" s="5">
+        <v>79</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.08708227405491703</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04021832664989211</v>
+      </c>
+      <c r="R3" s="5">
+        <v>79</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.1749163184551215</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1749163184551215</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1739942495016074</v>
+      </c>
+      <c r="E4" s="4">
+        <v>100</v>
+      </c>
+      <c r="F4" s="4">
+        <v>100</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1749163184551215</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1749163184551215</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.3239682859675597</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.3239682859675597</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.3225853389994811</v>
+      </c>
+      <c r="E5" s="4">
+        <v>100</v>
+      </c>
+      <c r="F5" s="4">
+        <v>100</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3239682859675597</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3239682859675597</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.512232234346925</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.512232234346925</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.5103884242654431</v>
+      </c>
+      <c r="E6" s="4">
+        <v>100</v>
+      </c>
+      <c r="F6" s="4">
+        <v>100</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.512232234346925</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.512232234346925</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>87.2340425531915</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>12.76595744680851</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>12.76595744680851</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.07935179223872191</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.05300217062782225</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.0498143766273562</v>
+      </c>
+      <c r="K3" s="4">
+        <v>88.86741930814875</v>
+      </c>
+      <c r="L3" s="4">
+        <v>89.66573849302711</v>
+      </c>
+      <c r="M3" s="5">
+        <v>94</v>
+      </c>
+      <c r="N3" s="5">
+        <v>167897.6113796234</v>
+      </c>
+      <c r="O3" s="4">
+        <v>32.17045629040494</v>
+      </c>
+      <c r="P3" s="5">
+        <v>5219</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>90.42553191489363</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>9.574468085106384</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1.063829787234043</v>
+      </c>
+      <c r="F4" s="3">
+        <v>8.51063829787234</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.1480665498345877</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.1313389239107719</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.108376771779938</v>
+      </c>
+      <c r="K4" s="4">
+        <v>83.26639166304793</v>
+      </c>
+      <c r="L4" s="4">
+        <v>85.43897853300773</v>
+      </c>
+      <c r="M4" s="5">
+        <v>94</v>
+      </c>
+      <c r="N4" s="5">
+        <v>609966.726064682</v>
+      </c>
+      <c r="O4" s="4">
+        <v>53.97935628890991</v>
+      </c>
+      <c r="P4" s="5">
+        <v>11300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>87.2340425531915</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>12.76595744680851</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>12.76595744680851</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.09216288049621765</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.06539271836328441</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.0724323538004726</v>
+      </c>
+      <c r="K5" s="4">
+        <v>85.59921841076869</v>
+      </c>
+      <c r="L5" s="4">
+        <v>89.34468561092828</v>
+      </c>
+      <c r="M5" s="5">
+        <v>94</v>
+      </c>
+      <c r="N5" s="5">
+        <v>951269.8812484741</v>
+      </c>
+      <c r="O5" s="4">
+        <v>137.0310978462221</v>
+      </c>
+      <c r="P5" s="5">
+        <v>6942</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>76.59574468085107</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2.127659574468085</v>
+      </c>
+      <c r="D6" s="3">
+        <v>21.27659574468085</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>21.27659574468085</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.1609583513216662</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.1319650604032369</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.1528668759448812</v>
+      </c>
+      <c r="K6" s="4">
+        <v>84.05123751628318</v>
+      </c>
+      <c r="L6" s="4">
+        <v>82.20417440144773</v>
+      </c>
+      <c r="M6" s="5">
+        <v>94</v>
+      </c>
+      <c r="N6" s="5">
+        <v>1207932.188510895</v>
+      </c>
+      <c r="O6" s="4">
+        <v>83.0079843671588</v>
+      </c>
+      <c r="P6" s="5">
+        <v>14552</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>91.48936170212765</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>8.51063829787234</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>8.51063829787234</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.09105147124546528</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.05283906240862001</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.05006315198926777</v>
+      </c>
+      <c r="K7" s="4">
+        <v>89.05449413808087</v>
+      </c>
+      <c r="L7" s="4">
+        <v>91.57813318101707</v>
+      </c>
+      <c r="M7" s="5">
+        <v>94</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1077139.176607132</v>
+      </c>
+      <c r="O7" s="4">
+        <v>183.2492644789268</v>
+      </c>
+      <c r="P7" s="5">
+        <v>5878</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>87.2340425531915</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>12.76595744680851</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2.127659574468085</v>
+      </c>
+      <c r="F8" s="3">
+        <v>10.63829787234043</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.09877437792305591</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.05485783417761481</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.05084892806579393</v>
+      </c>
+      <c r="K8" s="4">
+        <v>89.47170357504703</v>
+      </c>
+      <c r="L8" s="4">
+        <v>91.11809224618021</v>
+      </c>
+      <c r="M8" s="5">
+        <v>94</v>
+      </c>
+      <c r="N8" s="5">
+        <v>139183.956861496</v>
+      </c>
+      <c r="O8" s="4">
+        <v>15.05016834575</v>
+      </c>
+      <c r="P8" s="5">
+        <v>9248</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>74.46808510638297</v>
+      </c>
+      <c r="C9" s="3">
+        <v>6.382978723404255</v>
+      </c>
+      <c r="D9" s="3">
+        <v>19.14893617021277</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4.25531914893617</v>
+      </c>
+      <c r="F9" s="3">
+        <v>14.8936170212766</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.1323772494233083</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.08155188268548201</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.09099729589029398</v>
+      </c>
+      <c r="K9" s="4">
+        <v>81.1065277174699</v>
+      </c>
+      <c r="L9" s="4">
+        <v>82.89375981722108</v>
+      </c>
+      <c r="M9" s="5">
+        <v>94</v>
+      </c>
+      <c r="N9" s="5">
+        <v>448401.5810489655</v>
+      </c>
+      <c r="O9" s="4">
+        <v>29.37641385278862</v>
+      </c>
+      <c r="P9" s="5">
+        <v>15264</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>87.2340425531915</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>12.76595744680851</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>12.76595744680851</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.1303962940193077</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.09505048210735666</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.08311112849295463</v>
+      </c>
+      <c r="K10" s="4">
+        <v>83.08619192357806</v>
+      </c>
+      <c r="L10" s="4">
+        <v>87.22606977961793</v>
+      </c>
+      <c r="M10" s="5">
+        <v>94</v>
+      </c>
+      <c r="N10" s="5">
+        <v>615654.7989845276</v>
+      </c>
+      <c r="O10" s="4">
+        <v>82.15302895443389</v>
+      </c>
+      <c r="P10" s="5">
+        <v>7494</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>93.61702127659575</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>6.382978723404255</v>
+      </c>
+      <c r="E11" s="3">
+        <v>3.191489361702128</v>
+      </c>
+      <c r="F11" s="3">
+        <v>3.191489361702128</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.105228797665737</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.07896691053093603</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.07254814598079264</v>
+      </c>
+      <c r="K11" s="4">
+        <v>88.767911419887</v>
+      </c>
+      <c r="L11" s="4">
+        <v>91.7064115379125</v>
+      </c>
+      <c r="M11" s="5">
+        <v>94</v>
+      </c>
+      <c r="N11" s="5">
+        <v>405536.0078811646</v>
+      </c>
+      <c r="O11" s="4">
+        <v>40.61045542571245</v>
+      </c>
+      <c r="P11" s="5">
+        <v>9986</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>88.29787234042553</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>11.70212765957447</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1.063829787234043</v>
+      </c>
+      <c r="F12" s="3">
+        <v>10.63829787234043</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.0951104989187999</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.06700587920750778</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.06592371239699905</v>
+      </c>
+      <c r="K12" s="4">
+        <v>86.03343465045589</v>
+      </c>
+      <c r="L12" s="4">
+        <v>89.03672235708531</v>
+      </c>
+      <c r="M12" s="5">
+        <v>94</v>
+      </c>
+      <c r="N12" s="5">
+        <v>132947.0331668854</v>
+      </c>
+      <c r="O12" s="4">
+        <v>19.03867007974873</v>
+      </c>
+      <c r="P12" s="5">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>97.87234042553192</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>2.127659574468085</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>2.127659574468085</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.05427563114194689</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.05034520849143186</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.0489812353262915</v>
+      </c>
+      <c r="K13" s="4">
+        <v>85.55796786799827</v>
+      </c>
+      <c r="L13" s="4">
+        <v>90.99671569327367</v>
+      </c>
+      <c r="M13" s="5">
+        <v>94</v>
+      </c>
+      <c r="N13" s="5">
+        <v>445218.0774211884</v>
+      </c>
+      <c r="O13" s="4">
+        <v>71.41772175508315</v>
+      </c>
+      <c r="P13" s="5">
+        <v>6234</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>95.74468085106383</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>4.25531914893617</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>4.25531914893617</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.09454166731701012</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.06734940803173611</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.06475042326490321</v>
+      </c>
+      <c r="K14" s="4">
+        <v>97.42726877985254</v>
+      </c>
+      <c r="L14" s="4">
+        <v>96.97938978532866</v>
+      </c>
+      <c r="M14" s="5">
+        <v>94</v>
+      </c>
+      <c r="N14" s="5">
+        <v>686291.4917469025</v>
+      </c>
+      <c r="O14" s="4">
+        <v>266.0044541654661</v>
+      </c>
+      <c r="P14" s="5">
+        <v>2580</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>91.48936170212765</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>8.51063829787234</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1.063829787234043</v>
+      </c>
+      <c r="F15" s="3">
+        <v>7.446808510638298</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.07073048014955377</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.03657724600447532</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.03716471545705132</v>
+      </c>
+      <c r="K15" s="4">
+        <v>85.39224200318436</v>
+      </c>
+      <c r="L15" s="4">
+        <v>90.10721595506614</v>
+      </c>
+      <c r="M15" s="5">
+        <v>94</v>
+      </c>
+      <c r="N15" s="5">
+        <v>3542382.23195076</v>
+      </c>
+      <c r="O15" s="4">
+        <v>269.7724645457894</v>
+      </c>
+      <c r="P15" s="5">
+        <v>13131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>87.2340425531915</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>12.76595744680851</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>12.76595744680851</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.09964130799242231</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.07339642650546178</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.06740164019670987</v>
+      </c>
+      <c r="K16" s="4">
+        <v>95.68389057750755</v>
+      </c>
+      <c r="L16" s="4">
+        <v>92.85865581417542</v>
+      </c>
+      <c r="M16" s="5">
+        <v>94</v>
+      </c>
+      <c r="N16" s="5">
+        <v>303180.4075241089</v>
+      </c>
+      <c r="O16" s="4">
+        <v>100.0595404369996</v>
+      </c>
+      <c r="P16" s="5">
+        <v>3030</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>87.2340425531915</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>12.76595744680851</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>12.76595744680851</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.09505961465709635</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.05107761761111076</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.04795401910479948</v>
+      </c>
+      <c r="K17" s="4">
+        <v>84.79555652048066</v>
+      </c>
+      <c r="L17" s="4">
+        <v>88.48136512922997</v>
+      </c>
+      <c r="M17" s="5">
+        <v>94</v>
+      </c>
+      <c r="N17" s="5">
+        <v>633282.6075553894</v>
+      </c>
+      <c r="O17" s="4">
+        <v>96.87664181664211</v>
+      </c>
+      <c r="P17" s="5">
+        <v>6537</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3581,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
         <v>6</v>
@@ -3757,10 +6135,10 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
@@ -3801,16 +6179,16 @@
         <v>2</v>
       </c>
       <c r="K9" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M9" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N9" s="5">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="25" customHeight="1">
@@ -3895,10 +6273,10 @@
         <v>2</v>
       </c>
       <c r="M11" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N11" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="25" customHeight="1">
@@ -3939,10 +6317,10 @@
         <v>5</v>
       </c>
       <c r="M12" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="25" customHeight="1">
@@ -4065,13 +6443,13 @@
         <v>0</v>
       </c>
       <c r="K15" s="5">
+        <v>1</v>
+      </c>
+      <c r="L15" s="5">
         <v>2</v>
       </c>
-      <c r="L15" s="5">
-        <v>3</v>
-      </c>
       <c r="M15" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N15" s="5">
         <v>4</v>
@@ -4178,9 +6556,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>82</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>12</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>12</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>8</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>85</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>9</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5">
+        <v>8</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>6</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>82</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>12</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>12</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>6</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>72</v>
+      </c>
+      <c r="C6" s="5">
+        <v>2</v>
+      </c>
+      <c r="D6" s="5">
+        <v>20</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>20</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>2</v>
+      </c>
+      <c r="L6" s="5">
+        <v>10</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>86</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>8</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>8</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>4</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>82</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>12</v>
+      </c>
+      <c r="E8" s="5">
+        <v>2</v>
+      </c>
+      <c r="F8" s="5">
+        <v>10</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>2</v>
+      </c>
+      <c r="I8" s="5">
+        <v>2</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>4</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>70</v>
+      </c>
+      <c r="C9" s="5">
+        <v>6</v>
+      </c>
+      <c r="D9" s="5">
+        <v>18</v>
+      </c>
+      <c r="E9" s="5">
+        <v>4</v>
+      </c>
+      <c r="F9" s="5">
+        <v>14</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>4</v>
+      </c>
+      <c r="I9" s="5">
+        <v>2</v>
+      </c>
+      <c r="J9" s="5">
+        <v>2</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>10</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>82</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>12</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>12</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>6</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>88</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>6</v>
+      </c>
+      <c r="E11" s="5">
+        <v>3</v>
+      </c>
+      <c r="F11" s="5">
+        <v>3</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>3</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>3</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>2</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>83</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>11</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5">
+        <v>10</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>1</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>5</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>92</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>2</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>2</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>2</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>90</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>4</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>4</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>86</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>8</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1</v>
+      </c>
+      <c r="F15" s="5">
+        <v>7</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5">
+        <v>1</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>1</v>
+      </c>
+      <c r="L15" s="5">
+        <v>2</v>
+      </c>
+      <c r="M15" s="5">
+        <v>1</v>
+      </c>
+      <c r="N15" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>82</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>12</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>12</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>8</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>82</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>12</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>12</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>6</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4191,9 +7324,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4227,8 +7366,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4250,10 +7397,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3963415309725131</v>
@@ -4291,10 +7456,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.4017186081726691</v>
+      </c>
+      <c r="O3" s="5">
+        <v>79</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.07723898008766035</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04956780644327415</v>
+      </c>
+      <c r="R3" s="5">
+        <v>79</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.07323678473510498</v>
@@ -4332,19 +7515,35 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.07323678473510498</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.07323678473510498</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2158726953149426</v>
+        <v>0.1412118024127196</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2158726953149426</v>
+        <v>0.1412118024127196</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2120341561914074</v>
+        <v>0.1383343285815428</v>
       </c>
       <c r="E5" s="4">
         <v>100</v>
@@ -4373,19 +7572,35 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1412118024127196</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1412118024127196</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.1412118024127196</v>
+        <v>0.2158726953149426</v>
       </c>
       <c r="C6" s="4">
-        <v>0.1412118024127196</v>
+        <v>0.2158726953149426</v>
       </c>
       <c r="D6" s="4">
-        <v>0.1383343285815428</v>
+        <v>0.2120341561914074</v>
       </c>
       <c r="E6" s="4">
         <v>100</v>
@@ -4414,9 +7629,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2158726953149426</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.2158726953149426</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4427,14 +7658,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4445,9 +7677,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4481,8 +7719,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4504,10 +7750,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2386008123405131</v>
@@ -4545,10 +7809,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.212882730675423</v>
+      </c>
+      <c r="O3" s="5">
+        <v>82</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1362174270283989</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1175773013115691</v>
+      </c>
+      <c r="R3" s="5">
+        <v>82</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.1848224018005347</v>
@@ -4586,19 +7868,35 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1848224018005347</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1848224018005347</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.8736886285424816</v>
+        <v>0.4639587945239256</v>
       </c>
       <c r="C5" s="4">
-        <v>0.8736886285424816</v>
+        <v>0.4639587945239256</v>
       </c>
       <c r="D5" s="4">
-        <v>0.8629407189965832</v>
+        <v>0.4558926171557616</v>
       </c>
       <c r="E5" s="4">
         <v>100</v>
@@ -4627,19 +7925,35 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4639587945239256</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4639587945239256</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.4639587945239256</v>
+        <v>0.8736886285424816</v>
       </c>
       <c r="C6" s="4">
-        <v>0.4639587945239256</v>
+        <v>0.8736886285424816</v>
       </c>
       <c r="D6" s="4">
-        <v>0.4558926171557616</v>
+        <v>0.8629407189965832</v>
       </c>
       <c r="E6" s="4">
         <v>100</v>
@@ -4668,9 +7982,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.8736886285424816</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.8736886285424816</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4681,14 +8011,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4699,9 +8030,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4735,8 +8072,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4758,10 +8103,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3272037605526738</v>
@@ -4799,10 +8162,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3250298185050683</v>
+      </c>
+      <c r="O3" s="5">
+        <v>79</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.08223385267326126</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05293889534698274</v>
+      </c>
+      <c r="R3" s="5">
+        <v>79</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2087716672805762</v>
@@ -4840,19 +8221,35 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2087716672805762</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2087716672805762</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5983760856271374</v>
+        <v>0.3728824204699706</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5983760856271374</v>
+        <v>0.3728824204699706</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5925233267427075</v>
+        <v>0.3684932536380003</v>
       </c>
       <c r="E5" s="4">
         <v>100</v>
@@ -4881,19 +8278,35 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3728824204699706</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3728824204699706</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.3728824204699706</v>
+        <v>0.5983760856271374</v>
       </c>
       <c r="C6" s="4">
-        <v>0.3728824204699706</v>
+        <v>0.5983760856271374</v>
       </c>
       <c r="D6" s="4">
-        <v>0.3684932536380003</v>
+        <v>0.5925233267427075</v>
       </c>
       <c r="E6" s="4">
         <v>100</v>
@@ -4922,9 +8335,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.5983760856271374</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.5983760856271374</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4935,14 +8364,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4953,9 +8383,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4989,8 +8425,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5012,10 +8456,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2994512964475379</v>
@@ -5053,10 +8515,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3136670035635847</v>
+      </c>
+      <c r="O3" s="5">
+        <v>69</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.154292716721066</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1219135731364265</v>
+      </c>
+      <c r="R3" s="5">
+        <v>69</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.1519192073730444</v>
@@ -5094,19 +8574,35 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1519192073730444</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1519192073730444</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6136836312890637</v>
+        <v>0.3238449639575194</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6136836312890637</v>
+        <v>0.3238449639575194</v>
       </c>
       <c r="D5" s="4">
-        <v>0.6072387002587902</v>
+        <v>0.3190112656848143</v>
       </c>
       <c r="E5" s="4">
         <v>100</v>
@@ -5135,19 +8631,35 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3238449639575194</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3238449639575194</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.3238449639575194</v>
+        <v>0.6136836312890637</v>
       </c>
       <c r="C6" s="4">
-        <v>0.3238449639575194</v>
+        <v>0.6136836312890637</v>
       </c>
       <c r="D6" s="4">
-        <v>0.3190112656848143</v>
+        <v>0.6072387002587902</v>
       </c>
       <c r="E6" s="4">
         <v>100</v>
@@ -5176,9 +8688,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.6136836312890637</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.6136836312890637</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5189,14 +8717,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5207,9 +8736,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5243,8 +8778,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5266,10 +8809,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.276683531245824</v>
@@ -5307,10 +8868,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2507048514098247</v>
+      </c>
+      <c r="O3" s="5">
+        <v>83</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.07534737751628239</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.03424014968734074</v>
+      </c>
+      <c r="R3" s="5">
+        <v>83</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.3596776340393042</v>
@@ -5348,19 +8927,35 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3596776340393042</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3596776340393042</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.784878661501466</v>
+        <v>0.5576706475512694</v>
       </c>
       <c r="C5" s="4">
-        <v>0.784878661501466</v>
+        <v>0.5576706475512694</v>
       </c>
       <c r="D5" s="4">
-        <v>0.7797450326562512</v>
+        <v>0.5538192338244627</v>
       </c>
       <c r="E5" s="4">
         <v>100</v>
@@ -5389,19 +8984,35 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5576706475512694</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.5576706475512694</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.5576706475512694</v>
+        <v>0.784878661501466</v>
       </c>
       <c r="C6" s="4">
-        <v>0.5576706475512694</v>
+        <v>0.784878661501466</v>
       </c>
       <c r="D6" s="4">
-        <v>0.5538192338244627</v>
+        <v>0.7797450326562512</v>
       </c>
       <c r="E6" s="4">
         <v>100</v>
@@ -5430,9 +9041,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.784878661501466</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.784878661501466</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5443,514 +9070,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.3196715649670389</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.3022846986665534</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.3001057772792698</v>
-      </c>
-      <c r="E3" s="4">
-        <v>89.12461687971884</v>
-      </c>
-      <c r="F3" s="4">
-        <v>90.82528210044964</v>
-      </c>
-      <c r="G3" s="5">
-        <v>91</v>
-      </c>
-      <c r="H3" s="5">
-        <v>79</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>12</v>
-      </c>
-      <c r="K3" s="5">
-        <v>2</v>
-      </c>
-      <c r="L3" s="5">
-        <v>10</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.2437046173875945</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2437046173875945</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.2416405087687474</v>
-      </c>
-      <c r="E4" s="4">
-        <v>100</v>
-      </c>
-      <c r="F4" s="4">
-        <v>100</v>
-      </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.6057349674054997</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.6057349674054997</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.6016067501677913</v>
-      </c>
-      <c r="E5" s="4">
-        <v>100</v>
-      </c>
-      <c r="F5" s="4">
-        <v>100</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.421519007225676</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.421519007225676</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.4184228442974032</v>
-      </c>
-      <c r="E6" s="4">
-        <v>100</v>
-      </c>
-      <c r="F6" s="4">
-        <v>100</v>
-      </c>
-      <c r="G6" s="5">
-        <v>1</v>
-      </c>
-      <c r="H6" s="5">
-        <v>1</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.4107293980856612</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.4159873751647689</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.3780177021296857</v>
-      </c>
-      <c r="E3" s="4">
-        <v>80.48366599387005</v>
-      </c>
-      <c r="F3" s="4">
-        <v>82.32981783317355</v>
-      </c>
-      <c r="G3" s="5">
-        <v>91</v>
-      </c>
-      <c r="H3" s="5">
-        <v>67</v>
-      </c>
-      <c r="I3" s="5">
-        <v>6</v>
-      </c>
-      <c r="J3" s="5">
-        <v>18</v>
-      </c>
-      <c r="K3" s="5">
-        <v>4</v>
-      </c>
-      <c r="L3" s="5">
-        <v>14</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.204924902716062</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.204924902716062</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.203251204290769</v>
-      </c>
-      <c r="E4" s="4">
-        <v>100</v>
-      </c>
-      <c r="F4" s="4">
-        <v>100</v>
-      </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.3374852441430676</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.3374852441430676</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.3341378472924816</v>
-      </c>
-      <c r="E5" s="4">
-        <v>100</v>
-      </c>
-      <c r="F5" s="4">
-        <v>100</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.3112133092181395</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.3112133092181395</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.3087027615802</v>
-      </c>
-      <c r="E6" s="4">
-        <v>100</v>
-      </c>
-      <c r="F6" s="4">
-        <v>100</v>
-      </c>
-      <c r="G6" s="5">
-        <v>1</v>
-      </c>
-      <c r="H6" s="5">
-        <v>1</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/LandersUnderstanding2020.xlsx
+++ b/public/downloads/LandersUnderstanding2020.xlsx
@@ -1560,16 +1560,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2993017945856602</v>
+        <v>-0.3095310969079321</v>
       </c>
       <c r="O3" s="5">
         <v>79</v>
       </c>
       <c r="P3" s="4">
-        <v>0.08806409816207127</v>
+        <v>0.087823759928913</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.04085295962716005</v>
+        <v>0.04057611432061068</v>
       </c>
       <c r="R3" s="5">
         <v>79</v>
@@ -1913,16 +1913,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4123078265649519</v>
+        <v>-0.4264754909090698</v>
       </c>
       <c r="O3" s="5">
         <v>67</v>
       </c>
       <c r="P3" s="4">
-        <v>0.127360857029821</v>
+        <v>0.1283858797182312</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.07246281092397719</v>
+        <v>0.07216334450446059</v>
       </c>
       <c r="R3" s="5">
         <v>67</v>
@@ -2266,16 +2266,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.233914099630112</v>
+        <v>-0.2627937547173191</v>
       </c>
       <c r="O3" s="5">
         <v>79</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1200300971319361</v>
+        <v>0.1179049278634441</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08176742701258868</v>
+        <v>0.0793194472223004</v>
       </c>
       <c r="R3" s="5">
         <v>79</v>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2939896287584804</v>
+        <v>-0.2770404798648087</v>
       </c>
       <c r="O3" s="5">
         <v>85</v>
       </c>
       <c r="P3" s="4">
-        <v>0.09285420642672755</v>
+        <v>0.09166037249919962</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.06479192859970942</v>
+        <v>0.06391262754538357</v>
       </c>
       <c r="R3" s="5">
         <v>85</v>
@@ -2972,16 +2972,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2836016833318286</v>
+        <v>-0.3057838359745801</v>
       </c>
       <c r="O3" s="5">
         <v>80</v>
       </c>
       <c r="P3" s="4">
-        <v>0.08193265541058421</v>
+        <v>0.08120846731362091</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.05096215897773898</v>
+        <v>0.04986111810940885</v>
       </c>
       <c r="R3" s="5">
         <v>80</v>
@@ -3325,16 +3325,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4463232564121774</v>
+        <v>-0.4306789435904648</v>
       </c>
       <c r="O3" s="5">
         <v>89</v>
       </c>
       <c r="P3" s="4">
-        <v>0.05484772101337667</v>
+        <v>0.0534883479045775</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.05079766815826967</v>
+        <v>0.04905618974766125</v>
       </c>
       <c r="R3" s="5">
         <v>89</v>
@@ -3678,16 +3678,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.0872512832354172</v>
+        <v>-0.09207133252857602</v>
       </c>
       <c r="O3" s="5">
         <v>87</v>
       </c>
       <c r="P3" s="4">
-        <v>0.06578202343315963</v>
+        <v>0.06586835696350321</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.03632981755718188</v>
+        <v>0.036198508983488</v>
       </c>
       <c r="R3" s="5">
         <v>87</v>
@@ -4031,16 +4031,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3899699117785244</v>
+        <v>-0.3961278791866789</v>
       </c>
       <c r="O3" s="5">
         <v>83</v>
       </c>
       <c r="P3" s="4">
-        <v>0.06929573381371948</v>
+        <v>0.0685886528732319</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.03376975661897948</v>
+        <v>0.03284613854186287</v>
       </c>
       <c r="R3" s="5">
         <v>83</v>
@@ -4384,16 +4384,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.07525547677357627</v>
+        <v>-0.07371036502445352</v>
       </c>
       <c r="O3" s="5">
         <v>79</v>
       </c>
       <c r="P3" s="4">
-        <v>0.07013844041090508</v>
+        <v>0.06987607040563643</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.03841546961458903</v>
+        <v>0.03811324593763397</v>
       </c>
       <c r="R3" s="5">
         <v>79</v>
@@ -4737,16 +4737,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3026601245750693</v>
+        <v>-0.3083786347779096</v>
       </c>
       <c r="O3" s="5">
         <v>79</v>
       </c>
       <c r="P3" s="4">
-        <v>0.08708227405491703</v>
+        <v>0.08651675558149012</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.04021832664989211</v>
+        <v>0.03956690663619782</v>
       </c>
       <c r="R3" s="5">
         <v>79</v>
@@ -5054,13 +5054,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.07935179223872191</v>
+        <v>0.07804353880485203</v>
       </c>
       <c r="I3" s="4">
-        <v>0.05300217062782225</v>
+        <v>0.05150246547192265</v>
       </c>
       <c r="J3" s="4">
-        <v>0.0498143766273562</v>
+        <v>0.04792162755167752</v>
       </c>
       <c r="K3" s="4">
         <v>88.86741930814875</v>
@@ -5104,13 +5104,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.1480665498345877</v>
+        <v>0.1470867589235404</v>
       </c>
       <c r="I4" s="4">
-        <v>0.1313389239107719</v>
+        <v>0.1305412650333025</v>
       </c>
       <c r="J4" s="4">
-        <v>0.108376771779938</v>
+        <v>0.1086673076096236</v>
       </c>
       <c r="K4" s="4">
         <v>83.26639166304793</v>
@@ -5154,13 +5154,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.09216288049621765</v>
+        <v>0.09164782756530891</v>
       </c>
       <c r="I5" s="4">
-        <v>0.06539271836328441</v>
+        <v>0.06501746977323147</v>
       </c>
       <c r="J5" s="4">
-        <v>0.0724323538004726</v>
+        <v>0.07247928090451804</v>
       </c>
       <c r="K5" s="4">
         <v>85.59921841076869</v>
@@ -5204,13 +5204,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.1609583513216662</v>
+        <v>0.1565250856706264</v>
       </c>
       <c r="I6" s="4">
-        <v>0.1319650604032369</v>
+        <v>0.1300733277532028</v>
       </c>
       <c r="J6" s="4">
-        <v>0.1528668759448812</v>
+        <v>0.1448394712720547</v>
       </c>
       <c r="K6" s="4">
         <v>84.05123751628318</v>
@@ -5254,13 +5254,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.09105147124546528</v>
+        <v>0.0908736763302966</v>
       </c>
       <c r="I7" s="4">
-        <v>0.05283906240862001</v>
+        <v>0.05264472843157517</v>
       </c>
       <c r="J7" s="4">
-        <v>0.05006315198926777</v>
+        <v>0.05215352908495967</v>
       </c>
       <c r="K7" s="4">
         <v>89.05449413808087</v>
@@ -5304,13 +5304,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.09877437792305591</v>
+        <v>0.098541710059041</v>
       </c>
       <c r="I8" s="4">
-        <v>0.05485783417761481</v>
+        <v>0.05459111735789041</v>
       </c>
       <c r="J8" s="4">
-        <v>0.05084892806579393</v>
+        <v>0.05030892879536392</v>
       </c>
       <c r="K8" s="4">
         <v>89.47170357504703</v>
@@ -5354,13 +5354,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.1323772494233083</v>
+        <v>0.1333695586216629</v>
       </c>
       <c r="I9" s="4">
-        <v>0.08155188268548201</v>
+        <v>0.08126525054108755</v>
       </c>
       <c r="J9" s="4">
-        <v>0.09099729589029398</v>
+        <v>0.09499877034718139</v>
       </c>
       <c r="K9" s="4">
         <v>81.1065277174699</v>
@@ -5404,13 +5404,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.1303962940193077</v>
+        <v>0.1283389493019378</v>
       </c>
       <c r="I10" s="4">
-        <v>0.09505048210735666</v>
+        <v>0.09269206255329847</v>
       </c>
       <c r="J10" s="4">
-        <v>0.08311112849295463</v>
+        <v>0.08098696168454574</v>
       </c>
       <c r="K10" s="4">
         <v>83.08619192357806</v>
@@ -5454,13 +5454,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.105228797665737</v>
+        <v>0.1040730648210025</v>
       </c>
       <c r="I11" s="4">
-        <v>0.07896691053093603</v>
+        <v>0.07811758564891673</v>
       </c>
       <c r="J11" s="4">
-        <v>0.07254814598079264</v>
+        <v>0.07488734361705759</v>
       </c>
       <c r="K11" s="4">
         <v>88.767911419887</v>
@@ -5504,13 +5504,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.0951104989187999</v>
+        <v>0.09440942320790989</v>
       </c>
       <c r="I12" s="4">
-        <v>0.06700587920750778</v>
+        <v>0.0659446349970691</v>
       </c>
       <c r="J12" s="4">
-        <v>0.06592371239699905</v>
+        <v>0.06527049545822607</v>
       </c>
       <c r="K12" s="4">
         <v>86.03343465045589</v>
@@ -5554,13 +5554,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.05427563114194689</v>
+        <v>0.05295964228130089</v>
       </c>
       <c r="I13" s="4">
-        <v>0.05034520849143186</v>
+        <v>0.04866051742029981</v>
       </c>
       <c r="J13" s="4">
-        <v>0.0489812353262915</v>
+        <v>0.04860290849621199</v>
       </c>
       <c r="K13" s="4">
         <v>85.55796786799827</v>
@@ -5604,13 +5604,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.09454166731701012</v>
+        <v>0.09462524552191721</v>
       </c>
       <c r="I14" s="4">
-        <v>0.06734940803173611</v>
+        <v>0.06722247641049869</v>
       </c>
       <c r="J14" s="4">
-        <v>0.06475042326490321</v>
+        <v>0.06490425462532318</v>
       </c>
       <c r="K14" s="4">
         <v>97.42726877985254</v>
@@ -5654,13 +5654,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.07073048014955377</v>
+        <v>0.07004596562206047</v>
       </c>
       <c r="I15" s="4">
-        <v>0.03657724600447532</v>
+        <v>0.03568584716260697</v>
       </c>
       <c r="J15" s="4">
-        <v>0.03716471545705132</v>
+        <v>0.03659320863981173</v>
       </c>
       <c r="K15" s="4">
         <v>85.39224200318436</v>
@@ -5704,13 +5704,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.09964130799242231</v>
+        <v>0.0993873114979601</v>
       </c>
       <c r="I16" s="4">
-        <v>0.07339642650546178</v>
+        <v>0.07310525979229777</v>
       </c>
       <c r="J16" s="4">
-        <v>0.06740164019670987</v>
+        <v>0.06708933037507867</v>
       </c>
       <c r="K16" s="4">
         <v>95.68389057750755</v>
@@ -5754,13 +5754,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.09505961465709635</v>
+        <v>0.09451214464558731</v>
       </c>
       <c r="I17" s="4">
-        <v>0.05107761761111076</v>
+        <v>0.05045003003694187</v>
       </c>
       <c r="J17" s="4">
-        <v>0.04795401910479948</v>
+        <v>0.04772938244666782</v>
       </c>
       <c r="K17" s="4">
         <v>84.79555652048066</v>
@@ -7457,16 +7457,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4017186081726691</v>
+        <v>-0.4165717182258959</v>
       </c>
       <c r="O3" s="5">
         <v>79</v>
       </c>
       <c r="P3" s="4">
-        <v>0.07723898008766035</v>
+        <v>0.07588759741970685</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.04956780644327415</v>
+        <v>0.04801115045866949</v>
       </c>
       <c r="R3" s="5">
         <v>79</v>
@@ -7810,16 +7810,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.212882730675423</v>
+        <v>-0.2371820717289665</v>
       </c>
       <c r="O3" s="5">
         <v>82</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1362174270283989</v>
+        <v>0.1352053353180863</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1175773013115691</v>
+        <v>0.1167504597922411</v>
       </c>
       <c r="R3" s="5">
         <v>82</v>
@@ -8163,16 +8163,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3250298185050683</v>
+        <v>-0.320618670724798</v>
       </c>
       <c r="O3" s="5">
         <v>79</v>
       </c>
       <c r="P3" s="4">
-        <v>0.08223385267326126</v>
+        <v>0.08170181997539949</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.05293889534698274</v>
+        <v>0.05254939681047211</v>
       </c>
       <c r="R3" s="5">
         <v>79</v>
@@ -8516,16 +8516,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3136670035635847</v>
+        <v>-0.2754497940768488</v>
       </c>
       <c r="O3" s="5">
         <v>69</v>
       </c>
       <c r="P3" s="4">
-        <v>0.154292716721066</v>
+        <v>0.1497132994551566</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1219135731364265</v>
+        <v>0.1199395912407388</v>
       </c>
       <c r="R3" s="5">
         <v>69</v>
@@ -8869,16 +8869,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2507048514098247</v>
+        <v>-0.2650867483716866</v>
       </c>
       <c r="O3" s="5">
         <v>83</v>
       </c>
       <c r="P3" s="4">
-        <v>0.07534737751628239</v>
+        <v>0.07516372123028396</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.03424014968734074</v>
+        <v>0.03403879159064367</v>
       </c>
       <c r="R3" s="5">
         <v>83</v>
